--- a/data/trans_camb/IP07_R-Dificultad-trans_camb.xlsx
+++ b/data/trans_camb/IP07_R-Dificultad-trans_camb.xlsx
@@ -40,7 +40,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="12">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -66,13 +66,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin"/>
-      <bottom style="thin"/>
       <diagonal/>
     </border>
     <border>
@@ -513,7 +506,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K34"/>
+  <dimension ref="A1:H34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -524,9 +517,6 @@
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -542,68 +532,50 @@
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
-      <c r="E1" s="3" t="n"/>
-      <c r="F1" s="3" t="inlineStr">
+      <c r="E1" s="3" t="inlineStr">
         <is>
           <t>Niña</t>
         </is>
       </c>
-      <c r="G1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
       <c r="H1" s="3" t="n"/>
-      <c r="I1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="J1" s="3" t="n"/>
-      <c r="K1" s="3" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="n"/>
       <c r="B2" s="2" t="n"/>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>2012/2007</t>
+          <t>2016/2012</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>2016/2007</t>
+          <t>2023/2012</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>2023/2007</t>
+          <t>2016/2012</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>2012/2007</t>
+          <t>2023/2012</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>2016/2007</t>
+          <t>2016/2012</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>2023/2007</t>
-        </is>
-      </c>
-      <c r="I2" s="3" t="inlineStr">
-        <is>
-          <t>2012/2007</t>
-        </is>
-      </c>
-      <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>2016/2007</t>
-        </is>
-      </c>
-      <c r="K2" s="3" t="inlineStr">
-        <is>
-          <t>2023/2007</t>
+          <t>2023/2012</t>
         </is>
       </c>
     </row>
@@ -616,9 +588,6 @@
       <c r="F3" s="2" t="n"/>
       <c r="G3" s="2" t="n"/>
       <c r="H3" s="2" t="n"/>
-      <c r="I3" s="2" t="n"/>
-      <c r="J3" s="2" t="n"/>
-      <c r="K3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -631,15 +600,24 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr"/>
-      <c r="D4" s="5" t="inlineStr"/>
-      <c r="E4" s="5" t="inlineStr"/>
-      <c r="F4" s="5" t="inlineStr"/>
-      <c r="G4" s="5" t="inlineStr"/>
-      <c r="H4" s="5" t="inlineStr"/>
-      <c r="I4" s="5" t="inlineStr"/>
-      <c r="J4" s="5" t="inlineStr"/>
-      <c r="K4" s="5" t="inlineStr"/>
+      <c r="C4" s="5" t="n">
+        <v>13.07600858368458</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>8.327097582211017</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>4.992743220799511</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>-5.603748540189446</v>
+      </c>
+      <c r="G4" s="5" t="n">
+        <v>9.110961491180959</v>
+      </c>
+      <c r="H4" s="5" t="n">
+        <v>1.619590269681859</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
@@ -648,15 +626,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr"/>
-      <c r="D5" s="5" t="inlineStr"/>
-      <c r="E5" s="5" t="inlineStr"/>
-      <c r="F5" s="5" t="inlineStr"/>
-      <c r="G5" s="5" t="inlineStr"/>
-      <c r="H5" s="5" t="inlineStr"/>
-      <c r="I5" s="5" t="inlineStr"/>
-      <c r="J5" s="5" t="inlineStr"/>
-      <c r="K5" s="5" t="inlineStr"/>
+      <c r="C5" s="5" t="n">
+        <v>7.198518487531722</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-0.6851741985499865</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>-0.4533325647460033</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>-15.01717287649233</v>
+      </c>
+      <c r="G5" s="5" t="n">
+        <v>4.618436321717287</v>
+      </c>
+      <c r="H5" s="5" t="n">
+        <v>-4.393411805392308</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n"/>
@@ -665,15 +652,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C6" s="5" t="inlineStr"/>
-      <c r="D6" s="5" t="inlineStr"/>
-      <c r="E6" s="5" t="inlineStr"/>
-      <c r="F6" s="5" t="inlineStr"/>
-      <c r="G6" s="5" t="inlineStr"/>
-      <c r="H6" s="5" t="inlineStr"/>
-      <c r="I6" s="5" t="inlineStr"/>
-      <c r="J6" s="5" t="inlineStr"/>
-      <c r="K6" s="5" t="inlineStr"/>
+      <c r="C6" s="5" t="n">
+        <v>19.99700817140964</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>16.71117986288231</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>10.57287134812982</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>2.807863223579397</v>
+      </c>
+      <c r="G6" s="5" t="n">
+        <v>13.00097321067276</v>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>8.148281168565314</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n"/>
@@ -682,15 +678,24 @@
           <t>Cambio relativo (%)</t>
         </is>
       </c>
-      <c r="C7" s="6" t="inlineStr"/>
-      <c r="D7" s="6" t="inlineStr"/>
-      <c r="E7" s="6" t="inlineStr"/>
-      <c r="F7" s="6" t="inlineStr"/>
-      <c r="G7" s="6" t="inlineStr"/>
-      <c r="H7" s="6" t="inlineStr"/>
-      <c r="I7" s="6" t="inlineStr"/>
-      <c r="J7" s="6" t="inlineStr"/>
-      <c r="K7" s="6" t="inlineStr"/>
+      <c r="C7" s="6" t="n">
+        <v>0.1873327978323948</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>0.1192977564916371</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>0.06311117169318767</v>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>-0.07083463350809233</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>0.1225416242698701</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>0.02178334553280685</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n"/>
@@ -699,15 +704,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C8" s="6" t="inlineStr"/>
-      <c r="D8" s="6" t="inlineStr"/>
-      <c r="E8" s="6" t="inlineStr"/>
-      <c r="F8" s="6" t="inlineStr"/>
-      <c r="G8" s="6" t="inlineStr"/>
-      <c r="H8" s="6" t="inlineStr"/>
-      <c r="I8" s="6" t="inlineStr"/>
-      <c r="J8" s="6" t="inlineStr"/>
-      <c r="K8" s="6" t="inlineStr"/>
+      <c r="C8" s="6" t="n">
+        <v>0.1005792188282697</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>-0.00796610454244475</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>-0.005777259456403955</v>
+      </c>
+      <c r="F8" s="6" t="n">
+        <v>-0.1883886413524348</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>0.05987560530043259</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>-0.05787414938455255</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
@@ -716,15 +730,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C9" s="6" t="inlineStr"/>
-      <c r="D9" s="6" t="inlineStr"/>
-      <c r="E9" s="6" t="inlineStr"/>
-      <c r="F9" s="6" t="inlineStr"/>
-      <c r="G9" s="6" t="inlineStr"/>
-      <c r="H9" s="6" t="inlineStr"/>
-      <c r="I9" s="6" t="inlineStr"/>
-      <c r="J9" s="6" t="inlineStr"/>
-      <c r="K9" s="6" t="inlineStr"/>
+      <c r="C9" s="6" t="n">
+        <v>0.3048616709912125</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>0.2537339502812251</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>0.1395111549198194</v>
+      </c>
+      <c r="F9" s="6" t="n">
+        <v>0.03636472984926255</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>0.182587913125613</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>0.1121789695666103</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
@@ -737,15 +760,24 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C10" s="5" t="inlineStr"/>
-      <c r="D10" s="5" t="inlineStr"/>
-      <c r="E10" s="5" t="inlineStr"/>
-      <c r="F10" s="5" t="inlineStr"/>
-      <c r="G10" s="5" t="inlineStr"/>
-      <c r="H10" s="5" t="inlineStr"/>
-      <c r="I10" s="5" t="inlineStr"/>
-      <c r="J10" s="5" t="inlineStr"/>
-      <c r="K10" s="5" t="inlineStr"/>
+      <c r="C10" s="5" t="n">
+        <v>12.09687629638919</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>-0.06418455734016337</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>16.52638784028833</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>5.148057978334963</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>14.30897327413445</v>
+      </c>
+      <c r="H10" s="5" t="n">
+        <v>2.45062573643986</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
@@ -754,15 +786,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr"/>
-      <c r="D11" s="5" t="inlineStr"/>
-      <c r="E11" s="5" t="inlineStr"/>
-      <c r="F11" s="5" t="inlineStr"/>
-      <c r="G11" s="5" t="inlineStr"/>
-      <c r="H11" s="5" t="inlineStr"/>
-      <c r="I11" s="5" t="inlineStr"/>
-      <c r="J11" s="5" t="inlineStr"/>
-      <c r="K11" s="5" t="inlineStr"/>
+      <c r="C11" s="5" t="n">
+        <v>6.0080795741094</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-11.8566738062605</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>10.77528516434845</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>-2.411949185002698</v>
+      </c>
+      <c r="G11" s="5" t="n">
+        <v>10.46632896533266</v>
+      </c>
+      <c r="H11" s="5" t="n">
+        <v>-3.949470291717652</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n"/>
@@ -771,15 +812,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C12" s="5" t="inlineStr"/>
-      <c r="D12" s="5" t="inlineStr"/>
-      <c r="E12" s="5" t="inlineStr"/>
-      <c r="F12" s="5" t="inlineStr"/>
-      <c r="G12" s="5" t="inlineStr"/>
-      <c r="H12" s="5" t="inlineStr"/>
-      <c r="I12" s="5" t="inlineStr"/>
-      <c r="J12" s="5" t="inlineStr"/>
-      <c r="K12" s="5" t="inlineStr"/>
+      <c r="C12" s="5" t="n">
+        <v>18.27988441927183</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>7.589880465082683</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>22.76011176963221</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>12.05814115132191</v>
+      </c>
+      <c r="G12" s="5" t="n">
+        <v>18.76985463845953</v>
+      </c>
+      <c r="H12" s="5" t="n">
+        <v>7.572103870070142</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n"/>
@@ -788,15 +838,24 @@
           <t>Cambio relativo (%)</t>
         </is>
       </c>
-      <c r="C13" s="6" t="inlineStr"/>
-      <c r="D13" s="6" t="inlineStr"/>
-      <c r="E13" s="6" t="inlineStr"/>
-      <c r="F13" s="6" t="inlineStr"/>
-      <c r="G13" s="6" t="inlineStr"/>
-      <c r="H13" s="6" t="inlineStr"/>
-      <c r="I13" s="6" t="inlineStr"/>
-      <c r="J13" s="6" t="inlineStr"/>
-      <c r="K13" s="6" t="inlineStr"/>
+      <c r="C13" s="6" t="n">
+        <v>0.1609462502074754</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>-0.0008539612683490425</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>0.2255158571271093</v>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>0.07024939259225371</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>0.1927872960055012</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>0.03301770855241946</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n"/>
@@ -805,15 +864,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C14" s="6" t="inlineStr"/>
-      <c r="D14" s="6" t="inlineStr"/>
-      <c r="E14" s="6" t="inlineStr"/>
-      <c r="F14" s="6" t="inlineStr"/>
-      <c r="G14" s="6" t="inlineStr"/>
-      <c r="H14" s="6" t="inlineStr"/>
-      <c r="I14" s="6" t="inlineStr"/>
-      <c r="J14" s="6" t="inlineStr"/>
-      <c r="K14" s="6" t="inlineStr"/>
+      <c r="C14" s="6" t="n">
+        <v>0.07726798495030458</v>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>-0.1579923194351442</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>0.1428964550251495</v>
+      </c>
+      <c r="F14" s="6" t="n">
+        <v>-0.0302700820399777</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>0.1368260498182747</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>-0.05232010440237097</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
@@ -822,15 +890,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C15" s="6" t="inlineStr"/>
-      <c r="D15" s="6" t="inlineStr"/>
-      <c r="E15" s="6" t="inlineStr"/>
-      <c r="F15" s="6" t="inlineStr"/>
-      <c r="G15" s="6" t="inlineStr"/>
-      <c r="H15" s="6" t="inlineStr"/>
-      <c r="I15" s="6" t="inlineStr"/>
-      <c r="J15" s="6" t="inlineStr"/>
-      <c r="K15" s="6" t="inlineStr"/>
+      <c r="C15" s="6" t="n">
+        <v>0.2573648694617316</v>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>0.1043089445083244</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>0.3323408304457287</v>
+      </c>
+      <c r="F15" s="6" t="n">
+        <v>0.1720018996084769</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>0.26296379010732</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>0.1034447788321039</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
@@ -843,15 +920,24 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C16" s="5" t="inlineStr"/>
-      <c r="D16" s="5" t="inlineStr"/>
-      <c r="E16" s="5" t="inlineStr"/>
-      <c r="F16" s="5" t="inlineStr"/>
-      <c r="G16" s="5" t="inlineStr"/>
-      <c r="H16" s="5" t="inlineStr"/>
-      <c r="I16" s="5" t="inlineStr"/>
-      <c r="J16" s="5" t="inlineStr"/>
-      <c r="K16" s="5" t="inlineStr"/>
+      <c r="C16" s="5" t="n">
+        <v>15.24093199516136</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>0.4588849500353764</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>17.12817458683953</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>0.05993921582160278</v>
+      </c>
+      <c r="G16" s="5" t="n">
+        <v>16.18129532950664</v>
+      </c>
+      <c r="H16" s="5" t="n">
+        <v>0.3222146689874639</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n"/>
@@ -860,15 +946,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C17" s="5" t="inlineStr"/>
-      <c r="D17" s="5" t="inlineStr"/>
-      <c r="E17" s="5" t="inlineStr"/>
-      <c r="F17" s="5" t="inlineStr"/>
-      <c r="G17" s="5" t="inlineStr"/>
-      <c r="H17" s="5" t="inlineStr"/>
-      <c r="I17" s="5" t="inlineStr"/>
-      <c r="J17" s="5" t="inlineStr"/>
-      <c r="K17" s="5" t="inlineStr"/>
+      <c r="C17" s="5" t="n">
+        <v>8.813104309884077</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>-6.623609734145313</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>10.26793593322157</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>-7.838653289519708</v>
+      </c>
+      <c r="G17" s="5" t="n">
+        <v>11.58557338216459</v>
+      </c>
+      <c r="H17" s="5" t="n">
+        <v>-5.285819797435887</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n"/>
@@ -877,15 +972,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C18" s="5" t="inlineStr"/>
-      <c r="D18" s="5" t="inlineStr"/>
-      <c r="E18" s="5" t="inlineStr"/>
-      <c r="F18" s="5" t="inlineStr"/>
-      <c r="G18" s="5" t="inlineStr"/>
-      <c r="H18" s="5" t="inlineStr"/>
-      <c r="I18" s="5" t="inlineStr"/>
-      <c r="J18" s="5" t="inlineStr"/>
-      <c r="K18" s="5" t="inlineStr"/>
+      <c r="C18" s="5" t="n">
+        <v>21.50823635272308</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>7.860990153296063</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>24.154444731589</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>7.878302357810485</v>
+      </c>
+      <c r="G18" s="5" t="n">
+        <v>20.54689004319864</v>
+      </c>
+      <c r="H18" s="5" t="n">
+        <v>5.327449937249469</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n"/>
@@ -894,15 +998,24 @@
           <t>Cambio relativo (%)</t>
         </is>
       </c>
-      <c r="C19" s="6" t="inlineStr"/>
-      <c r="D19" s="6" t="inlineStr"/>
-      <c r="E19" s="6" t="inlineStr"/>
-      <c r="F19" s="6" t="inlineStr"/>
-      <c r="G19" s="6" t="inlineStr"/>
-      <c r="H19" s="6" t="inlineStr"/>
-      <c r="I19" s="6" t="inlineStr"/>
-      <c r="J19" s="6" t="inlineStr"/>
-      <c r="K19" s="6" t="inlineStr"/>
+      <c r="C19" s="6" t="n">
+        <v>0.2009845277481005</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>0.006051386818263563</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>0.229021241068312</v>
+      </c>
+      <c r="F19" s="6" t="n">
+        <v>0.0008014487198578833</v>
+      </c>
+      <c r="G19" s="6" t="n">
+        <v>0.2148387822467481</v>
+      </c>
+      <c r="H19" s="6" t="n">
+        <v>0.004278038667341743</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n"/>
@@ -911,15 +1024,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C20" s="6" t="inlineStr"/>
-      <c r="D20" s="6" t="inlineStr"/>
-      <c r="E20" s="6" t="inlineStr"/>
-      <c r="F20" s="6" t="inlineStr"/>
-      <c r="G20" s="6" t="inlineStr"/>
-      <c r="H20" s="6" t="inlineStr"/>
-      <c r="I20" s="6" t="inlineStr"/>
-      <c r="J20" s="6" t="inlineStr"/>
-      <c r="K20" s="6" t="inlineStr"/>
+      <c r="C20" s="6" t="n">
+        <v>0.1090527341960429</v>
+      </c>
+      <c r="D20" s="6" t="n">
+        <v>-0.08492959906728849</v>
+      </c>
+      <c r="E20" s="6" t="n">
+        <v>0.1295229086538966</v>
+      </c>
+      <c r="F20" s="6" t="n">
+        <v>-0.09986563070696848</v>
+      </c>
+      <c r="G20" s="6" t="n">
+        <v>0.1468985757404319</v>
+      </c>
+      <c r="H20" s="6" t="n">
+        <v>-0.06716120228283068</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n"/>
@@ -928,15 +1050,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C21" s="6" t="inlineStr"/>
-      <c r="D21" s="6" t="inlineStr"/>
-      <c r="E21" s="6" t="inlineStr"/>
-      <c r="F21" s="6" t="inlineStr"/>
-      <c r="G21" s="6" t="inlineStr"/>
-      <c r="H21" s="6" t="inlineStr"/>
-      <c r="I21" s="6" t="inlineStr"/>
-      <c r="J21" s="6" t="inlineStr"/>
-      <c r="K21" s="6" t="inlineStr"/>
+      <c r="C21" s="6" t="n">
+        <v>0.2976706452380679</v>
+      </c>
+      <c r="D21" s="6" t="n">
+        <v>0.1101655158939776</v>
+      </c>
+      <c r="E21" s="6" t="n">
+        <v>0.3430788967903227</v>
+      </c>
+      <c r="F21" s="6" t="n">
+        <v>0.1107083911977662</v>
+      </c>
+      <c r="G21" s="6" t="n">
+        <v>0.2887056663061424</v>
+      </c>
+      <c r="H21" s="6" t="n">
+        <v>0.07432198065460453</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
@@ -949,15 +1080,24 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C22" s="5" t="inlineStr"/>
-      <c r="D22" s="5" t="inlineStr"/>
-      <c r="E22" s="5" t="inlineStr"/>
-      <c r="F22" s="5" t="inlineStr"/>
-      <c r="G22" s="5" t="inlineStr"/>
-      <c r="H22" s="5" t="inlineStr"/>
-      <c r="I22" s="5" t="inlineStr"/>
-      <c r="J22" s="5" t="inlineStr"/>
-      <c r="K22" s="5" t="inlineStr"/>
+      <c r="C22" s="5" t="n">
+        <v>1.144424763709839</v>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>-8.497704419236962</v>
+      </c>
+      <c r="E22" s="5" t="n">
+        <v>15.58454695090329</v>
+      </c>
+      <c r="F22" s="5" t="n">
+        <v>9.317715544353112</v>
+      </c>
+      <c r="G22" s="5" t="n">
+        <v>7.66119829814077</v>
+      </c>
+      <c r="H22" s="5" t="n">
+        <v>-0.2828237144129275</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n"/>
@@ -966,15 +1106,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C23" s="5" t="inlineStr"/>
-      <c r="D23" s="5" t="inlineStr"/>
-      <c r="E23" s="5" t="inlineStr"/>
-      <c r="F23" s="5" t="inlineStr"/>
-      <c r="G23" s="5" t="inlineStr"/>
-      <c r="H23" s="5" t="inlineStr"/>
-      <c r="I23" s="5" t="inlineStr"/>
-      <c r="J23" s="5" t="inlineStr"/>
-      <c r="K23" s="5" t="inlineStr"/>
+      <c r="C23" s="5" t="n">
+        <v>-7.430988189072712</v>
+      </c>
+      <c r="D23" s="5" t="n">
+        <v>-17.48001994722662</v>
+      </c>
+      <c r="E23" s="5" t="n">
+        <v>4.994416220413026</v>
+      </c>
+      <c r="F23" s="5" t="n">
+        <v>-0.3805154831092821</v>
+      </c>
+      <c r="G23" s="5" t="n">
+        <v>0.5455108966532041</v>
+      </c>
+      <c r="H23" s="5" t="n">
+        <v>-6.954634638146357</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n"/>
@@ -983,15 +1132,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C24" s="5" t="inlineStr"/>
-      <c r="D24" s="5" t="inlineStr"/>
-      <c r="E24" s="5" t="inlineStr"/>
-      <c r="F24" s="5" t="inlineStr"/>
-      <c r="G24" s="5" t="inlineStr"/>
-      <c r="H24" s="5" t="inlineStr"/>
-      <c r="I24" s="5" t="inlineStr"/>
-      <c r="J24" s="5" t="inlineStr"/>
-      <c r="K24" s="5" t="inlineStr"/>
+      <c r="C24" s="5" t="n">
+        <v>9.938358474661301</v>
+      </c>
+      <c r="D24" s="5" t="n">
+        <v>0.7485787205717411</v>
+      </c>
+      <c r="E24" s="5" t="n">
+        <v>26.4957154012154</v>
+      </c>
+      <c r="F24" s="5" t="n">
+        <v>19.66962946673022</v>
+      </c>
+      <c r="G24" s="5" t="n">
+        <v>14.6003557133891</v>
+      </c>
+      <c r="H24" s="5" t="n">
+        <v>7.148737610456317</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n"/>
@@ -1000,15 +1158,24 @@
           <t>Cambio relativo (%)</t>
         </is>
       </c>
-      <c r="C25" s="6" t="inlineStr"/>
-      <c r="D25" s="6" t="inlineStr"/>
-      <c r="E25" s="6" t="inlineStr"/>
-      <c r="F25" s="6" t="inlineStr"/>
-      <c r="G25" s="6" t="inlineStr"/>
-      <c r="H25" s="6" t="inlineStr"/>
-      <c r="I25" s="6" t="inlineStr"/>
-      <c r="J25" s="6" t="inlineStr"/>
-      <c r="K25" s="6" t="inlineStr"/>
+      <c r="C25" s="6" t="n">
+        <v>0.01391803217781937</v>
+      </c>
+      <c r="D25" s="6" t="n">
+        <v>-0.1033456521520403</v>
+      </c>
+      <c r="E25" s="6" t="n">
+        <v>0.2274406202664553</v>
+      </c>
+      <c r="F25" s="6" t="n">
+        <v>0.1359825864396547</v>
+      </c>
+      <c r="G25" s="6" t="n">
+        <v>0.100760929119523</v>
+      </c>
+      <c r="H25" s="6" t="n">
+        <v>-0.003719728837745531</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n"/>
@@ -1017,15 +1184,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C26" s="6" t="inlineStr"/>
-      <c r="D26" s="6" t="inlineStr"/>
-      <c r="E26" s="6" t="inlineStr"/>
-      <c r="F26" s="6" t="inlineStr"/>
-      <c r="G26" s="6" t="inlineStr"/>
-      <c r="H26" s="6" t="inlineStr"/>
-      <c r="I26" s="6" t="inlineStr"/>
-      <c r="J26" s="6" t="inlineStr"/>
-      <c r="K26" s="6" t="inlineStr"/>
+      <c r="C26" s="6" t="n">
+        <v>-0.08644489266593139</v>
+      </c>
+      <c r="D26" s="6" t="n">
+        <v>-0.2046031276859288</v>
+      </c>
+      <c r="E26" s="6" t="n">
+        <v>0.06694396033473783</v>
+      </c>
+      <c r="F26" s="6" t="n">
+        <v>-0.005378965486530219</v>
+      </c>
+      <c r="G26" s="6" t="n">
+        <v>0.006294283089946819</v>
+      </c>
+      <c r="H26" s="6" t="n">
+        <v>-0.08775965547422834</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n"/>
@@ -1034,15 +1210,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C27" s="6" t="inlineStr"/>
-      <c r="D27" s="6" t="inlineStr"/>
-      <c r="E27" s="6" t="inlineStr"/>
-      <c r="F27" s="6" t="inlineStr"/>
-      <c r="G27" s="6" t="inlineStr"/>
-      <c r="H27" s="6" t="inlineStr"/>
-      <c r="I27" s="6" t="inlineStr"/>
-      <c r="J27" s="6" t="inlineStr"/>
-      <c r="K27" s="6" t="inlineStr"/>
+      <c r="C27" s="6" t="n">
+        <v>0.1346397797421437</v>
+      </c>
+      <c r="D27" s="6" t="n">
+        <v>0.008926742535351388</v>
+      </c>
+      <c r="E27" s="6" t="n">
+        <v>0.4435587089873534</v>
+      </c>
+      <c r="F27" s="6" t="n">
+        <v>0.3216251646601713</v>
+      </c>
+      <c r="G27" s="6" t="n">
+        <v>0.2009366462598901</v>
+      </c>
+      <c r="H27" s="6" t="n">
+        <v>0.1008875912830169</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
@@ -1055,15 +1240,24 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C28" s="5" t="inlineStr"/>
-      <c r="D28" s="5" t="inlineStr"/>
-      <c r="E28" s="5" t="inlineStr"/>
-      <c r="F28" s="5" t="inlineStr"/>
-      <c r="G28" s="5" t="inlineStr"/>
-      <c r="H28" s="5" t="inlineStr"/>
-      <c r="I28" s="5" t="inlineStr"/>
-      <c r="J28" s="5" t="inlineStr"/>
-      <c r="K28" s="5" t="inlineStr"/>
+      <c r="C28" s="5" t="n">
+        <v>11.39708106705284</v>
+      </c>
+      <c r="D28" s="5" t="n">
+        <v>1.251105284814458</v>
+      </c>
+      <c r="E28" s="5" t="n">
+        <v>12.36935645400586</v>
+      </c>
+      <c r="F28" s="5" t="n">
+        <v>1.38151314810514</v>
+      </c>
+      <c r="G28" s="5" t="n">
+        <v>11.86515310554126</v>
+      </c>
+      <c r="H28" s="5" t="n">
+        <v>1.298607021890918</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n"/>
@@ -1072,15 +1266,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C29" s="5" t="inlineStr"/>
-      <c r="D29" s="5" t="inlineStr"/>
-      <c r="E29" s="5" t="inlineStr"/>
-      <c r="F29" s="5" t="inlineStr"/>
-      <c r="G29" s="5" t="inlineStr"/>
-      <c r="H29" s="5" t="inlineStr"/>
-      <c r="I29" s="5" t="inlineStr"/>
-      <c r="J29" s="5" t="inlineStr"/>
-      <c r="K29" s="5" t="inlineStr"/>
+      <c r="C29" s="5" t="n">
+        <v>8.362807534302698</v>
+      </c>
+      <c r="D29" s="5" t="n">
+        <v>-3.710795588553808</v>
+      </c>
+      <c r="E29" s="5" t="n">
+        <v>8.921714242463175</v>
+      </c>
+      <c r="F29" s="5" t="n">
+        <v>-2.922623858789062</v>
+      </c>
+      <c r="G29" s="5" t="n">
+        <v>9.729925902617955</v>
+      </c>
+      <c r="H29" s="5" t="n">
+        <v>-1.715384216017881</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n"/>
@@ -1089,15 +1292,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C30" s="5" t="inlineStr"/>
-      <c r="D30" s="5" t="inlineStr"/>
-      <c r="E30" s="5" t="inlineStr"/>
-      <c r="F30" s="5" t="inlineStr"/>
-      <c r="G30" s="5" t="inlineStr"/>
-      <c r="H30" s="5" t="inlineStr"/>
-      <c r="I30" s="5" t="inlineStr"/>
-      <c r="J30" s="5" t="inlineStr"/>
-      <c r="K30" s="5" t="inlineStr"/>
+      <c r="C30" s="5" t="n">
+        <v>15.0483521306781</v>
+      </c>
+      <c r="D30" s="5" t="n">
+        <v>5.031835636810655</v>
+      </c>
+      <c r="E30" s="5" t="n">
+        <v>15.64415688690869</v>
+      </c>
+      <c r="F30" s="5" t="n">
+        <v>5.296298880082595</v>
+      </c>
+      <c r="G30" s="5" t="n">
+        <v>14.61492689357078</v>
+      </c>
+      <c r="H30" s="5" t="n">
+        <v>4.147058071297126</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n"/>
@@ -1106,15 +1318,24 @@
           <t>Cambio relativo (%)</t>
         </is>
       </c>
-      <c r="C31" s="6" t="inlineStr"/>
-      <c r="D31" s="6" t="inlineStr"/>
-      <c r="E31" s="6" t="inlineStr"/>
-      <c r="F31" s="6" t="inlineStr"/>
-      <c r="G31" s="6" t="inlineStr"/>
-      <c r="H31" s="6" t="inlineStr"/>
-      <c r="I31" s="6" t="inlineStr"/>
-      <c r="J31" s="6" t="inlineStr"/>
-      <c r="K31" s="6" t="inlineStr"/>
+      <c r="C31" s="6" t="n">
+        <v>0.1532109561328289</v>
+      </c>
+      <c r="D31" s="6" t="n">
+        <v>0.01681860783313928</v>
+      </c>
+      <c r="E31" s="6" t="n">
+        <v>0.164725372845704</v>
+      </c>
+      <c r="F31" s="6" t="n">
+        <v>0.01839790689669728</v>
+      </c>
+      <c r="G31" s="6" t="n">
+        <v>0.1587708337112695</v>
+      </c>
+      <c r="H31" s="6" t="n">
+        <v>0.01737701298035837</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="n"/>
@@ -1123,15 +1344,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C32" s="6" t="inlineStr"/>
-      <c r="D32" s="6" t="inlineStr"/>
-      <c r="E32" s="6" t="inlineStr"/>
-      <c r="F32" s="6" t="inlineStr"/>
-      <c r="G32" s="6" t="inlineStr"/>
-      <c r="H32" s="6" t="inlineStr"/>
-      <c r="I32" s="6" t="inlineStr"/>
-      <c r="J32" s="6" t="inlineStr"/>
-      <c r="K32" s="6" t="inlineStr"/>
+      <c r="C32" s="6" t="n">
+        <v>0.1092438647734169</v>
+      </c>
+      <c r="D32" s="6" t="n">
+        <v>-0.04907473615404906</v>
+      </c>
+      <c r="E32" s="6" t="n">
+        <v>0.1156413968990645</v>
+      </c>
+      <c r="F32" s="6" t="n">
+        <v>-0.0383081223095289</v>
+      </c>
+      <c r="G32" s="6" t="n">
+        <v>0.127125890148798</v>
+      </c>
+      <c r="H32" s="6" t="n">
+        <v>-0.02260366751332945</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="n"/>
@@ -1140,15 +1370,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C33" s="6" t="inlineStr"/>
-      <c r="D33" s="6" t="inlineStr"/>
-      <c r="E33" s="6" t="inlineStr"/>
-      <c r="F33" s="6" t="inlineStr"/>
-      <c r="G33" s="6" t="inlineStr"/>
-      <c r="H33" s="6" t="inlineStr"/>
-      <c r="I33" s="6" t="inlineStr"/>
-      <c r="J33" s="6" t="inlineStr"/>
-      <c r="K33" s="6" t="inlineStr"/>
+      <c r="C33" s="6" t="n">
+        <v>0.2093348054912023</v>
+      </c>
+      <c r="D33" s="6" t="n">
+        <v>0.06911390571269739</v>
+      </c>
+      <c r="E33" s="6" t="n">
+        <v>0.2145898178239101</v>
+      </c>
+      <c r="F33" s="6" t="n">
+        <v>0.0719286791850567</v>
+      </c>
+      <c r="G33" s="6" t="n">
+        <v>0.2006420076612468</v>
+      </c>
+      <c r="H33" s="6" t="n">
+        <v>0.05630488181659889</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1159,11 +1398,11 @@
     </row>
   </sheetData>
   <mergeCells count="9">
-    <mergeCell ref="C1:E1"/>
     <mergeCell ref="A22:A27"/>
     <mergeCell ref="A4:A9"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="E1:F1"/>
     <mergeCell ref="A16:A21"/>
     <mergeCell ref="A10:A15"/>
     <mergeCell ref="A28:A33"/>
